--- a/Biểu mẫu báo cáo.xlsx
+++ b/Biểu mẫu báo cáo.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\OneDrive - ptit.edu.vn\Documents\Rikkei\IT215-K25\Session01\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\OneDrive - ptit.edu.vn\Documents\Rikkei\IT215-K25\Session03\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BF9191A-D641-4FE3-B29B-E661DD2334C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0E34F0F-4D5E-4C39-902D-2AC20E30E938}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2655" yWindow="2175" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3360" yWindow="2445" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ss01" sheetId="1" r:id="rId1"/>
@@ -31,32 +31,20 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="27">
   <si>
     <t>STT</t>
   </si>
   <si>
-    <t>Mức yêu cầu</t>
-  </si>
-  <si>
-    <t>Số lượng bài tập yêu cầu</t>
-  </si>
-  <si>
     <t>Số lượng bài tập hoàn thành</t>
   </si>
   <si>
-    <t>Mức hoàn thành</t>
-  </si>
-  <si>
     <t>Kết quả</t>
   </si>
   <si>
     <t>Nhận xét của nhóm trưởng/nhóm phó</t>
   </si>
   <si>
-    <t>Đề xuất (Nếu có)</t>
-  </si>
-  <si>
     <t>Nguyễn Hữu Đại</t>
   </si>
   <si>
@@ -96,12 +84,6 @@
     <t>Nhóm: 4</t>
   </si>
   <si>
-    <t>Session: 1</t>
-  </si>
-  <si>
-    <t>Ngày báo cáo: 05/07/2026</t>
-  </si>
-  <si>
     <t>IT215 - FASTAPI</t>
   </si>
   <si>
@@ -121,6 +103,15 @@
   </si>
   <si>
     <t>Nhóm trưởng: Đỗ Trung Hiếu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Có xin phép </t>
+  </si>
+  <si>
+    <t>Session: 3</t>
+  </si>
+  <si>
+    <t>Ngày báo cáo: 07/07/2026</t>
   </si>
 </sst>
 </file>
@@ -274,20 +265,20 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -571,8 +562,8 @@
     <col min="2" max="2" width="25.5" style="1" customWidth="1"/>
     <col min="3" max="3" width="12.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="15.5" style="1" customWidth="1"/>
-    <col min="5" max="5" width="18.125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="17.125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="46.75" style="1" customWidth="1"/>
+    <col min="6" max="6" width="39.75" style="1" customWidth="1"/>
     <col min="7" max="7" width="18.125" style="1" customWidth="1"/>
     <col min="8" max="8" width="38.125" style="1" customWidth="1"/>
     <col min="9" max="9" width="29.875" style="1" customWidth="1"/>
@@ -583,52 +574,46 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="38.65" customHeight="1">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+    </row>
+    <row r="3" spans="1:14" ht="20.25">
+      <c r="A3" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="18"/>
+      <c r="C3" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="18"/>
+      <c r="E3" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="G3" s="2"/>
+    </row>
+    <row r="4" spans="1:14" ht="20.25">
+      <c r="A4" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-    </row>
-    <row r="3" spans="1:14" ht="20.25">
-      <c r="A3" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="B3" s="17"/>
-      <c r="C3" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="F3" s="17"/>
-      <c r="G3" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="H3" s="17"/>
-    </row>
-    <row r="4" spans="1:14" ht="20.25">
-      <c r="A4" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="2"/>
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="2" t="s">
+        <v>26</v>
+      </c>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
     </row>
     <row r="5" spans="1:14" ht="20.25">
-      <c r="A5" s="18"/>
-      <c r="B5" s="18"/>
-      <c r="C5" s="18"/>
-      <c r="D5" s="18"/>
+      <c r="A5" s="17"/>
+      <c r="B5" s="17"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="17"/>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
@@ -637,12 +622,12 @@
       <c r="A6" s="3"/>
       <c r="B6" s="4"/>
     </row>
-    <row r="7" spans="1:14" ht="33">
+    <row r="7" spans="1:14" ht="49.5">
       <c r="A7" s="5" t="s">
         <v>0</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>1</v>
@@ -653,48 +638,30 @@
       <c r="E7" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="F7" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="I7" s="5" t="s">
-        <v>7</v>
-      </c>
+      <c r="I7" s="5"/>
     </row>
     <row r="8" spans="1:14">
       <c r="A8" s="6">
         <v>1</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6">
-        <v>1</v>
-      </c>
-      <c r="E8" s="6">
-        <v>1</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="H8" s="8" t="s">
-        <v>28</v>
+        <v>4</v>
+      </c>
+      <c r="C8" s="6">
+        <v>3</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>22</v>
       </c>
       <c r="I8" s="8"/>
       <c r="M8" s="9" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -702,30 +669,19 @@
         <v>2</v>
       </c>
       <c r="B9" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="8" t="s">
         <v>24</v>
-      </c>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6">
-        <v>1</v>
-      </c>
-      <c r="E9" s="6">
-        <v>1</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="H9" s="8" t="s">
-        <v>28</v>
       </c>
       <c r="I9" s="6"/>
       <c r="M9" s="11" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -733,30 +689,23 @@
         <v>3</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" s="6"/>
-      <c r="D10" s="6">
-        <v>1</v>
-      </c>
-      <c r="E10" s="6">
-        <v>1</v>
-      </c>
-      <c r="F10" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="G10" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="H10" s="8" t="s">
-        <v>28</v>
+      <c r="C10" s="6">
+        <v>3</v>
+      </c>
+      <c r="D10" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>22</v>
       </c>
       <c r="I10" s="6"/>
       <c r="M10" s="12" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -764,30 +713,23 @@
         <v>4</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6">
-        <v>1</v>
-      </c>
-      <c r="E11" s="6">
-        <v>1</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G11" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="H11" s="8" t="s">
-        <v>28</v>
+        <v>19</v>
+      </c>
+      <c r="C11" s="6">
+        <v>3</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>22</v>
       </c>
       <c r="I11" s="6"/>
       <c r="M11" s="13" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -795,23 +737,16 @@
         <v>5</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6">
-        <v>1</v>
-      </c>
-      <c r="E12" s="6">
-        <v>1</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G12" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="H12" s="8" t="s">
-        <v>28</v>
+        <v>20</v>
+      </c>
+      <c r="C12" s="6">
+        <v>3</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>22</v>
       </c>
       <c r="I12" s="6"/>
     </row>
@@ -820,41 +755,29 @@
         <v>6</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6">
-        <v>1</v>
-      </c>
-      <c r="E13" s="6">
-        <v>1</v>
-      </c>
-      <c r="F13" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G13" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="H13" s="8" t="s">
-        <v>28</v>
+        <v>21</v>
+      </c>
+      <c r="C13" s="6">
+        <v>3</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>22</v>
       </c>
       <c r="I13" s="14"/>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="5">
     <mergeCell ref="A4:D4"/>
     <mergeCell ref="A5:D5"/>
-    <mergeCell ref="A1:I1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="C3:D3"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="A1:E1"/>
   </mergeCells>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C8:C13 F8:F13" xr:uid="{00000000-0002-0000-0000-000000000000}">
-      <formula1>$M$8:$M$11</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G8:G9 G11:G13" xr:uid="{00000000-0002-0000-0000-000001000000}">
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D8:D9 D11:D13" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>$N$8:$N$11</formula1>
     </dataValidation>
   </dataValidations>
